--- a/GearSage-client/pkgGear/data_raw/bkk_hook_import.xlsx
+++ b/GearSage-client/pkgGear/data_raw/bkk_hook_import.xlsx
@@ -455,7 +455,7 @@
         <v/>
       </c>
       <c r="G2" t="str">
-        <v>wacky钩</v>
+        <v>Wacky/Neko钩</v>
       </c>
       <c r="H2" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/BKK_hooks/predator_wg_weedless.webp</v>
@@ -595,7 +595,7 @@
         <v/>
       </c>
       <c r="G6" t="str">
-        <v>wacky钩</v>
+        <v>Wacky/Neko钩</v>
       </c>
       <c r="H6" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/BKK_hooks/predator_wg.webp</v>
@@ -1330,7 +1330,7 @@
         <v/>
       </c>
       <c r="G27" t="str">
-        <v>Swimbait Hooks</v>
+        <v>Swimbait钩</v>
       </c>
       <c r="H27" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/BKK_hooks/straight_baitholder_chebu.webp</v>
@@ -1365,7 +1365,7 @@
         <v/>
       </c>
       <c r="G28" t="str">
-        <v>Swimbait Hooks</v>
+        <v>Swimbait钩</v>
       </c>
       <c r="H28" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/BKK_hooks/permalock_weighted.webp</v>
@@ -1400,7 +1400,7 @@
         <v/>
       </c>
       <c r="G29" t="str">
-        <v>Swimbait Hooks</v>
+        <v>Swimbait钩</v>
       </c>
       <c r="H29" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/BKK_hooks/permalock_hd.webp</v>
@@ -1435,7 +1435,7 @@
         <v/>
       </c>
       <c r="G30" t="str">
-        <v>Swimbait Hooks</v>
+        <v>Swimbait钩</v>
       </c>
       <c r="H30" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/BKK_hooks/permalock_tungsten_nail_keeper.webp</v>
@@ -1470,7 +1470,7 @@
         <v/>
       </c>
       <c r="G31" t="str">
-        <v>Swimbait Hooks</v>
+        <v>Swimbait钩</v>
       </c>
       <c r="H31" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/BKK_hooks/permalock.webp</v>
@@ -1505,7 +1505,7 @@
         <v/>
       </c>
       <c r="G32" t="str">
-        <v>Swimbait Hooks</v>
+        <v>曲柄钩</v>
       </c>
       <c r="H32" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/BKK_hooks/offset_worm_wg_hd.webp</v>
@@ -1540,7 +1540,7 @@
         <v/>
       </c>
       <c r="G33" t="str">
-        <v>Swimbait Hooks</v>
+        <v>曲柄钩</v>
       </c>
       <c r="H33" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/BKK_hooks/offset_worm_wg.webp</v>
@@ -1575,7 +1575,7 @@
         <v/>
       </c>
       <c r="G34" t="str">
-        <v>Swimbait Hooks</v>
+        <v>曲柄钩</v>
       </c>
       <c r="H34" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/BKK_hooks/offset_worm_round_bend.webp</v>
@@ -1610,7 +1610,7 @@
         <v/>
       </c>
       <c r="G35" t="str">
-        <v>Swimbait Hooks</v>
+        <v>曲柄钩</v>
       </c>
       <c r="H35" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/BKK_hooks/offset_worm_ewg_chebu.webp</v>
@@ -1645,7 +1645,7 @@
         <v/>
       </c>
       <c r="G36" t="str">
-        <v>Swimbait Hooks</v>
+        <v>曲柄钩</v>
       </c>
       <c r="H36" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/BKK_hooks/offset_worm_ewg.webp</v>
@@ -1680,7 +1680,7 @@
         <v/>
       </c>
       <c r="G37" t="str">
-        <v>Swimbait Hooks</v>
+        <v>Swimbait钩</v>
       </c>
       <c r="H37" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/BKK_hooks/mother_fluker.webp</v>
@@ -1715,7 +1715,7 @@
         <v/>
       </c>
       <c r="G38" t="str">
-        <v>Swimbait Hooks</v>
+        <v>直柄钩</v>
       </c>
       <c r="H38" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/BKK_hooks/heavy_cover_flipping_hook.webp</v>
@@ -1750,7 +1750,7 @@
         <v/>
       </c>
       <c r="G39" t="str">
-        <v>Swimbait Hooks</v>
+        <v>倒钓钩</v>
       </c>
       <c r="H39" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/BKK_hooks/dropshot_long_shank.webp</v>
@@ -1785,7 +1785,7 @@
         <v/>
       </c>
       <c r="G40" t="str">
-        <v>Swimbait Hooks</v>
+        <v>倒钓钩</v>
       </c>
       <c r="H40" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/BKK_hooks/dropshot.webp</v>
@@ -1820,7 +1820,7 @@
         <v/>
       </c>
       <c r="G41" t="str">
-        <v>Swimbait Hooks</v>
+        <v>特种钩</v>
       </c>
       <c r="H41" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/BKK_hooks/double_61_ss.webp</v>
@@ -1855,7 +1855,7 @@
         <v/>
       </c>
       <c r="G42" t="str">
-        <v>Swimbait Hooks</v>
+        <v>Swimbait钩</v>
       </c>
       <c r="H42" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/BKK_hooks/titandiver_gold.webp</v>
@@ -1890,7 +1890,7 @@
         <v/>
       </c>
       <c r="G43" t="str">
-        <v>Swimbait Hooks</v>
+        <v>Swimbait钩</v>
       </c>
       <c r="H43" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/BKK_hooks/titan_rider.webp</v>
@@ -1925,7 +1925,7 @@
         <v/>
       </c>
       <c r="G44" t="str">
-        <v>Swimbait Hooks</v>
+        <v>Swimbait钩</v>
       </c>
       <c r="H44" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/BKK_hooks/titan_diver.webp</v>
@@ -1960,7 +1960,7 @@
         <v/>
       </c>
       <c r="G45" t="str">
-        <v>Swimbait Hooks</v>
+        <v>Swimbait钩</v>
       </c>
       <c r="H45" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/BKK_hooks/titan_diver.webp</v>

--- a/GearSage-client/pkgGear/data_raw/bkk_hook_import.xlsx
+++ b/GearSage-client/pkgGear/data_raw/bkk_hook_import.xlsx
@@ -2044,7 +2044,7 @@
         <v>BKK</v>
       </c>
       <c r="D2" t="str">
-        <v>BHK1000-S4-Q6-N1</v>
+        <v>S4-Q6-N1</v>
       </c>
       <c r="E2" t="str">
         <v>wacky钩</v>
@@ -2091,7 +2091,7 @@
         <v>BKK</v>
       </c>
       <c r="D3" t="str">
-        <v>BHK1000-S2-Q6-N2</v>
+        <v>S2-Q6-N2</v>
       </c>
       <c r="E3" t="str">
         <v>wacky钩</v>
@@ -2138,7 +2138,7 @@
         <v>BKK</v>
       </c>
       <c r="D4" t="str">
-        <v>BHK1000-S1-Q6-N3</v>
+        <v>S1-Q6-N3</v>
       </c>
       <c r="E4" t="str">
         <v>wacky钩</v>
@@ -2185,7 +2185,7 @@
         <v>BKK</v>
       </c>
       <c r="D5" t="str">
-        <v>BHK1000-S1-0-Q6-N4</v>
+        <v>S1-0-Q6-N4</v>
       </c>
       <c r="E5" t="str">
         <v>wacky钩</v>
@@ -2232,7 +2232,7 @@
         <v>BKK</v>
       </c>
       <c r="D6" t="str">
-        <v>BHK1000-S2-0-Q6-N5</v>
+        <v>S2-0-Q6-N5</v>
       </c>
       <c r="E6" t="str">
         <v>wacky钩</v>
@@ -2279,7 +2279,7 @@
         <v>BKK</v>
       </c>
       <c r="D7" t="str">
-        <v>BHK1001-S2-0-Q4-N1</v>
+        <v>S2-0-Q4-N1</v>
       </c>
       <c r="E7" t="str">
         <v>直柄钩</v>
@@ -2326,7 +2326,7 @@
         <v>BKK</v>
       </c>
       <c r="D8" t="str">
-        <v>BHK1001-S3-0-Q4-N2</v>
+        <v>S3-0-Q4-N2</v>
       </c>
       <c r="E8" t="str">
         <v>直柄钩</v>
@@ -2373,7 +2373,7 @@
         <v>BKK</v>
       </c>
       <c r="D9" t="str">
-        <v>BHK1001-S4-0-Q4-N3</v>
+        <v>S4-0-Q4-N3</v>
       </c>
       <c r="E9" t="str">
         <v>直柄钩</v>
@@ -2420,7 +2420,7 @@
         <v>BKK</v>
       </c>
       <c r="D10" t="str">
-        <v>BHK1001-S5-0-Q4-N4</v>
+        <v>S5-0-Q4-N4</v>
       </c>
       <c r="E10" t="str">
         <v>直柄钩</v>
@@ -2467,7 +2467,7 @@
         <v>BKK</v>
       </c>
       <c r="D11" t="str">
-        <v>BHK1002-S2-Q6-N1</v>
+        <v>S2-Q6-N1</v>
       </c>
       <c r="E11" t="str">
         <v>倒钓钩</v>
@@ -2514,7 +2514,7 @@
         <v>BKK</v>
       </c>
       <c r="D12" t="str">
-        <v>BHK1002-S1-Q6-N2</v>
+        <v>S1-Q6-N2</v>
       </c>
       <c r="E12" t="str">
         <v>倒钓钩</v>
@@ -2561,7 +2561,7 @@
         <v>BKK</v>
       </c>
       <c r="D13" t="str">
-        <v>BHK1002-S1-0-Q5-N3</v>
+        <v>S1-0-Q5-N3</v>
       </c>
       <c r="E13" t="str">
         <v>倒钓钩</v>
@@ -2608,7 +2608,7 @@
         <v>BKK</v>
       </c>
       <c r="D14" t="str">
-        <v>BHK1002-S2-0-Q5-N4</v>
+        <v>S2-0-Q5-N4</v>
       </c>
       <c r="E14" t="str">
         <v>倒钓钩</v>
@@ -2655,7 +2655,7 @@
         <v>BKK</v>
       </c>
       <c r="D15" t="str">
-        <v>BHK1003-S6-Q7-N1</v>
+        <v>S6-Q7-N1</v>
       </c>
       <c r="E15" t="str">
         <v>倒钓钩</v>
@@ -2702,7 +2702,7 @@
         <v>BKK</v>
       </c>
       <c r="D16" t="str">
-        <v>BHK1003-S4-Q7-N2</v>
+        <v>S4-Q7-N2</v>
       </c>
       <c r="E16" t="str">
         <v>倒钓钩</v>
@@ -2749,7 +2749,7 @@
         <v>BKK</v>
       </c>
       <c r="D17" t="str">
-        <v>BHK1003-S2-Q7-N3</v>
+        <v>S2-Q7-N3</v>
       </c>
       <c r="E17" t="str">
         <v>倒钓钩</v>
@@ -2796,7 +2796,7 @@
         <v>BKK</v>
       </c>
       <c r="D18" t="str">
-        <v>BHK1003-S1-Q7-N4</v>
+        <v>S1-Q7-N4</v>
       </c>
       <c r="E18" t="str">
         <v>倒钓钩</v>
@@ -2843,7 +2843,7 @@
         <v>BKK</v>
       </c>
       <c r="D19" t="str">
-        <v>BHK1003-S1-0-Q6-N5</v>
+        <v>S1-0-Q6-N5</v>
       </c>
       <c r="E19" t="str">
         <v>倒钓钩</v>
@@ -2890,7 +2890,7 @@
         <v>BKK</v>
       </c>
       <c r="D20" t="str">
-        <v>BHK1003-S2-0-Q6-N6</v>
+        <v>S2-0-Q6-N6</v>
       </c>
       <c r="E20" t="str">
         <v>倒钓钩</v>
@@ -2937,7 +2937,7 @@
         <v>BKK</v>
       </c>
       <c r="D21" t="str">
-        <v>BHK1004-S4-Q6-N1</v>
+        <v>S4-Q6-N1</v>
       </c>
       <c r="E21" t="str">
         <v>wacky钩</v>
@@ -2984,7 +2984,7 @@
         <v>BKK</v>
       </c>
       <c r="D22" t="str">
-        <v>BHK1004-S2-Q6-N2</v>
+        <v>S2-Q6-N2</v>
       </c>
       <c r="E22" t="str">
         <v>wacky钩</v>
@@ -3031,7 +3031,7 @@
         <v>BKK</v>
       </c>
       <c r="D23" t="str">
-        <v>BHK1004-S1-Q6-N3</v>
+        <v>S1-Q6-N3</v>
       </c>
       <c r="E23" t="str">
         <v>wacky钩</v>
@@ -3078,7 +3078,7 @@
         <v>BKK</v>
       </c>
       <c r="D24" t="str">
-        <v>BHK1004-S1-0-Q6-N4</v>
+        <v>S1-0-Q6-N4</v>
       </c>
       <c r="E24" t="str">
         <v>wacky钩</v>
@@ -3125,7 +3125,7 @@
         <v>BKK</v>
       </c>
       <c r="D25" t="str">
-        <v>BHK1004-S2-0-Q6-N5</v>
+        <v>S2-0-Q6-N5</v>
       </c>
       <c r="E25" t="str">
         <v>wacky钩</v>
@@ -3172,7 +3172,7 @@
         <v>BKK</v>
       </c>
       <c r="D26" t="str">
-        <v>BHK1005-S6-Q10-N1</v>
+        <v>S6-Q10-N1</v>
       </c>
       <c r="E26" t="str">
         <v>曲柄钩</v>
@@ -3219,7 +3219,7 @@
         <v>BKK</v>
       </c>
       <c r="D27" t="str">
-        <v>BHK1005-S4-Q10-N2</v>
+        <v>S4-Q10-N2</v>
       </c>
       <c r="E27" t="str">
         <v>曲柄钩</v>
@@ -3266,7 +3266,7 @@
         <v>BKK</v>
       </c>
       <c r="D28" t="str">
-        <v>BHK1005-S2-Q9-N3</v>
+        <v>S2-Q9-N3</v>
       </c>
       <c r="E28" t="str">
         <v>曲柄钩</v>
@@ -3313,7 +3313,7 @@
         <v>BKK</v>
       </c>
       <c r="D29" t="str">
-        <v>BHK1005-S1-Q9-N4</v>
+        <v>S1-Q9-N4</v>
       </c>
       <c r="E29" t="str">
         <v>曲柄钩</v>
@@ -3360,7 +3360,7 @@
         <v>BKK</v>
       </c>
       <c r="D30" t="str">
-        <v>BHK1005-S1-0-Q9-N5</v>
+        <v>S1-0-Q9-N5</v>
       </c>
       <c r="E30" t="str">
         <v>曲柄钩</v>
@@ -3407,7 +3407,7 @@
         <v>BKK</v>
       </c>
       <c r="D31" t="str">
-        <v>BHK1005-S2-0-Q8-N6</v>
+        <v>S2-0-Q8-N6</v>
       </c>
       <c r="E31" t="str">
         <v>曲柄钩</v>
@@ -3454,7 +3454,7 @@
         <v>BKK</v>
       </c>
       <c r="D32" t="str">
-        <v>BHK1005-S3-0-Q8-N7</v>
+        <v>S3-0-Q8-N7</v>
       </c>
       <c r="E32" t="str">
         <v>曲柄钩</v>
@@ -3501,7 +3501,7 @@
         <v>BKK</v>
       </c>
       <c r="D33" t="str">
-        <v>BHK1006-S1-Q8-N1</v>
+        <v>S1-Q8-N1</v>
       </c>
       <c r="E33" t="str">
         <v>曲柄钩</v>
@@ -3548,7 +3548,7 @@
         <v>BKK</v>
       </c>
       <c r="D34" t="str">
-        <v>BHK1006-S1-0-Q8-N2</v>
+        <v>S1-0-Q8-N2</v>
       </c>
       <c r="E34" t="str">
         <v>曲柄钩</v>
@@ -3595,7 +3595,7 @@
         <v>BKK</v>
       </c>
       <c r="D35" t="str">
-        <v>BHK1006-S2-0-Q7-N3</v>
+        <v>S2-0-Q7-N3</v>
       </c>
       <c r="E35" t="str">
         <v>曲柄钩</v>
@@ -3642,7 +3642,7 @@
         <v>BKK</v>
       </c>
       <c r="D36" t="str">
-        <v>BHK1006-S3-0-Q7-N4</v>
+        <v>S3-0-Q7-N4</v>
       </c>
       <c r="E36" t="str">
         <v>曲柄钩</v>
@@ -3689,7 +3689,7 @@
         <v>BKK</v>
       </c>
       <c r="D37" t="str">
-        <v>BHK1006-S4-0-Q7-N5</v>
+        <v>S4-0-Q7-N5</v>
       </c>
       <c r="E37" t="str">
         <v>曲柄钩</v>
@@ -3736,7 +3736,7 @@
         <v>BKK</v>
       </c>
       <c r="D38" t="str">
-        <v>BHK1006-S5-0-Q6-N6</v>
+        <v>S5-0-Q6-N6</v>
       </c>
       <c r="E38" t="str">
         <v>曲柄钩</v>
@@ -3783,7 +3783,7 @@
         <v>BKK</v>
       </c>
       <c r="D39" t="str">
-        <v>BHK1007-S3-Q8-N1</v>
+        <v>S3-Q8-N1</v>
       </c>
       <c r="E39" t="str">
         <v>曲柄钩</v>
@@ -3830,7 +3830,7 @@
         <v>BKK</v>
       </c>
       <c r="D40" t="str">
-        <v>BHK1007-S2-Q8-N2</v>
+        <v>S2-Q8-N2</v>
       </c>
       <c r="E40" t="str">
         <v>曲柄钩</v>
@@ -3877,7 +3877,7 @@
         <v>BKK</v>
       </c>
       <c r="D41" t="str">
-        <v>BHK1007-S1-Q8-N3</v>
+        <v>S1-Q8-N3</v>
       </c>
       <c r="E41" t="str">
         <v>曲柄钩</v>
@@ -3924,7 +3924,7 @@
         <v>BKK</v>
       </c>
       <c r="D42" t="str">
-        <v>BHK1007-S1-0-Q7-N4</v>
+        <v>S1-0-Q7-N4</v>
       </c>
       <c r="E42" t="str">
         <v>曲柄钩</v>
@@ -3971,7 +3971,7 @@
         <v>BKK</v>
       </c>
       <c r="D43" t="str">
-        <v>BHK1007-S2-0-Q7-N5</v>
+        <v>S2-0-Q7-N5</v>
       </c>
       <c r="E43" t="str">
         <v>曲柄钩</v>
@@ -4018,7 +4018,7 @@
         <v>BKK</v>
       </c>
       <c r="D44" t="str">
-        <v>BHK1007-S3-0-Q6-N6</v>
+        <v>S3-0-Q6-N6</v>
       </c>
       <c r="E44" t="str">
         <v>曲柄钩</v>
@@ -4065,7 +4065,7 @@
         <v>BKK</v>
       </c>
       <c r="D45" t="str">
-        <v>BHK1007-S4-0-Q6-N7</v>
+        <v>S4-0-Q6-N7</v>
       </c>
       <c r="E45" t="str">
         <v>曲柄钩</v>
@@ -4112,7 +4112,7 @@
         <v>BKK</v>
       </c>
       <c r="D46" t="str">
-        <v>BHK1007-S5-0-Q5-N8</v>
+        <v>S5-0-Q5-N8</v>
       </c>
       <c r="E46" t="str">
         <v>曲柄钩</v>
@@ -4159,7 +4159,7 @@
         <v>BKK</v>
       </c>
       <c r="D47" t="str">
-        <v>BHK1007-S6-0-Q5-N9</v>
+        <v>S6-0-Q5-N9</v>
       </c>
       <c r="E47" t="str">
         <v>曲柄钩</v>
@@ -4206,7 +4206,7 @@
         <v>BKK</v>
       </c>
       <c r="D48" t="str">
-        <v>BHK1008-S1-Q7-N1</v>
+        <v>S1-Q7-N1</v>
       </c>
       <c r="E48" t="str">
         <v>曲柄钩</v>
@@ -4253,7 +4253,7 @@
         <v>BKK</v>
       </c>
       <c r="D49" t="str">
-        <v>BHK1008-S1-0-Q7-N2</v>
+        <v>S1-0-Q7-N2</v>
       </c>
       <c r="E49" t="str">
         <v>曲柄钩</v>
@@ -4300,7 +4300,7 @@
         <v>BKK</v>
       </c>
       <c r="D50" t="str">
-        <v>BHK1008-S2-0-Q6-N3</v>
+        <v>S2-0-Q6-N3</v>
       </c>
       <c r="E50" t="str">
         <v>曲柄钩</v>
@@ -4347,7 +4347,7 @@
         <v>BKK</v>
       </c>
       <c r="D51" t="str">
-        <v>BHK1008-S3-0-Q6-N4</v>
+        <v>S3-0-Q6-N4</v>
       </c>
       <c r="E51" t="str">
         <v>曲柄钩</v>
@@ -4394,7 +4394,7 @@
         <v>BKK</v>
       </c>
       <c r="D52" t="str">
-        <v>BHK1008-S4-0-Q6-N5</v>
+        <v>S4-0-Q6-N5</v>
       </c>
       <c r="E52" t="str">
         <v>曲柄钩</v>
@@ -4441,7 +4441,7 @@
         <v>BKK</v>
       </c>
       <c r="D53" t="str">
-        <v>BHK1008-S5-0-Q5-N6</v>
+        <v>S5-0-Q5-N6</v>
       </c>
       <c r="E53" t="str">
         <v>曲柄钩</v>
@@ -4488,7 +4488,7 @@
         <v>BKK</v>
       </c>
       <c r="D54" t="str">
-        <v>BHK1009-S1-Q8-N1</v>
+        <v>S1-Q8-N1</v>
       </c>
       <c r="E54" t="str">
         <v>曲柄钩</v>
@@ -4535,7 +4535,7 @@
         <v>BKK</v>
       </c>
       <c r="D55" t="str">
-        <v>BHK1009-S1-0-Q8-N2</v>
+        <v>S1-0-Q8-N2</v>
       </c>
       <c r="E55" t="str">
         <v>曲柄钩</v>
@@ -4582,7 +4582,7 @@
         <v>BKK</v>
       </c>
       <c r="D56" t="str">
-        <v>BHK1009-S2-0-Q7-N3</v>
+        <v>S2-0-Q7-N3</v>
       </c>
       <c r="E56" t="str">
         <v>曲柄钩</v>
@@ -4629,7 +4629,7 @@
         <v>BKK</v>
       </c>
       <c r="D57" t="str">
-        <v>BHK1009-S3-0-Q7-N4</v>
+        <v>S3-0-Q7-N4</v>
       </c>
       <c r="E57" t="str">
         <v>曲柄钩</v>
@@ -4676,7 +4676,7 @@
         <v>BKK</v>
       </c>
       <c r="D58" t="str">
-        <v>BHK1009-S4-0-Q6-N5</v>
+        <v>S4-0-Q6-N5</v>
       </c>
       <c r="E58" t="str">
         <v>曲柄钩</v>
@@ -4723,7 +4723,7 @@
         <v>BKK</v>
       </c>
       <c r="D59" t="str">
-        <v>BHK1009-S5-0-Q6-N6</v>
+        <v>S5-0-Q6-N6</v>
       </c>
       <c r="E59" t="str">
         <v>曲柄钩</v>
@@ -4770,7 +4770,7 @@
         <v>BKK</v>
       </c>
       <c r="D60" t="str">
-        <v>BHK1010-S1-0 (1-8oz)-N1</v>
+        <v>S1-0 (1-8oz)-N1</v>
       </c>
       <c r="E60" t="str">
         <v>铅头钩</v>
@@ -4817,7 +4817,7 @@
         <v>BKK</v>
       </c>
       <c r="D61" t="str">
-        <v>BHK1010-S1-0 (3-16oz)-N2</v>
+        <v>S1-0 (3-16oz)-N2</v>
       </c>
       <c r="E61" t="str">
         <v>铅头钩</v>
@@ -4864,7 +4864,7 @@
         <v>BKK</v>
       </c>
       <c r="D62" t="str">
-        <v>BHK1010-S1-0 (1-4oz)-N3</v>
+        <v>S1-0 (1-4oz)-N3</v>
       </c>
       <c r="E62" t="str">
         <v>铅头钩</v>
@@ -4911,7 +4911,7 @@
         <v>BKK</v>
       </c>
       <c r="D63" t="str">
-        <v>BHK1010-S1-0 (3-8oz)-N4</v>
+        <v>S1-0 (3-8oz)-N4</v>
       </c>
       <c r="E63" t="str">
         <v>铅头钩</v>
@@ -4958,7 +4958,7 @@
         <v>BKK</v>
       </c>
       <c r="D64" t="str">
-        <v>BHK1010-S3-0 (1-8oz)-N5</v>
+        <v>S3-0 (1-8oz)-N5</v>
       </c>
       <c r="E64" t="str">
         <v>铅头钩</v>
@@ -5005,7 +5005,7 @@
         <v>BKK</v>
       </c>
       <c r="D65" t="str">
-        <v>BHK1010-S3-0 (3-16oz)-N6</v>
+        <v>S3-0 (3-16oz)-N6</v>
       </c>
       <c r="E65" t="str">
         <v>铅头钩</v>
@@ -5052,7 +5052,7 @@
         <v>BKK</v>
       </c>
       <c r="D66" t="str">
-        <v>BHK1010-S3-0 (1-4oz)-N7</v>
+        <v>S3-0 (1-4oz)-N7</v>
       </c>
       <c r="E66" t="str">
         <v>铅头钩</v>
@@ -5099,7 +5099,7 @@
         <v>BKK</v>
       </c>
       <c r="D67" t="str">
-        <v>BHK1010-S3-0 (3-8oz)-N8</v>
+        <v>S3-0 (3-8oz)-N8</v>
       </c>
       <c r="E67" t="str">
         <v>铅头钩</v>
@@ -5146,7 +5146,7 @@
         <v>BKK</v>
       </c>
       <c r="D68" t="str">
-        <v>BHK1010-S5-0 (1-2oz)-N9</v>
+        <v>S5-0 (1-2oz)-N9</v>
       </c>
       <c r="E68" t="str">
         <v>铅头钩</v>
@@ -5193,7 +5193,7 @@
         <v>BKK</v>
       </c>
       <c r="D69" t="str">
-        <v>BHK1010-S5-0 (5-8oz)-N10</v>
+        <v>S5-0 (5-8oz)-N10</v>
       </c>
       <c r="E69" t="str">
         <v>铅头钩</v>
@@ -5240,7 +5240,7 @@
         <v>BKK</v>
       </c>
       <c r="D70" t="str">
-        <v>BHK1010-S5-0 (3-4oz)-N11</v>
+        <v>S5-0 (3-4oz)-N11</v>
       </c>
       <c r="E70" t="str">
         <v>铅头钩</v>
@@ -5287,7 +5287,7 @@
         <v>BKK</v>
       </c>
       <c r="D71" t="str">
-        <v>BHK1010-S5-0 (7-8oz)-N12</v>
+        <v>S5-0 (7-8oz)-N12</v>
       </c>
       <c r="E71" t="str">
         <v>铅头钩</v>
@@ -5334,7 +5334,7 @@
         <v>BKK</v>
       </c>
       <c r="D72" t="str">
-        <v>BHK1011-S1-0 (5g)-N1</v>
+        <v>S1-0 (5g)-N1</v>
       </c>
       <c r="E72" t="str">
         <v>铅头钩</v>
@@ -5381,7 +5381,7 @@
         <v>BKK</v>
       </c>
       <c r="D73" t="str">
-        <v>BHK1011-S1-0 (7.5g)-N2</v>
+        <v>S1-0 (7.5g)-N2</v>
       </c>
       <c r="E73" t="str">
         <v>铅头钩</v>
@@ -5428,7 +5428,7 @@
         <v>BKK</v>
       </c>
       <c r="D74" t="str">
-        <v>BHK1011-S1-0 (10g)-N3</v>
+        <v>S1-0 (10g)-N3</v>
       </c>
       <c r="E74" t="str">
         <v>铅头钩</v>
@@ -5475,7 +5475,7 @@
         <v>BKK</v>
       </c>
       <c r="D75" t="str">
-        <v>BHK1011-S2-0 (5g)-N4</v>
+        <v>S2-0 (5g)-N4</v>
       </c>
       <c r="E75" t="str">
         <v>铅头钩</v>
@@ -5522,7 +5522,7 @@
         <v>BKK</v>
       </c>
       <c r="D76" t="str">
-        <v>BHK1011-S2-0 (7.5g)-N5</v>
+        <v>S2-0 (7.5g)-N5</v>
       </c>
       <c r="E76" t="str">
         <v>铅头钩</v>
@@ -5569,7 +5569,7 @@
         <v>BKK</v>
       </c>
       <c r="D77" t="str">
-        <v>BHK1011-S2-0 (10g)-N6</v>
+        <v>S2-0 (10g)-N6</v>
       </c>
       <c r="E77" t="str">
         <v>铅头钩</v>
@@ -5616,7 +5616,7 @@
         <v>BKK</v>
       </c>
       <c r="D78" t="str">
-        <v>BHK1011-S2-0 (15g)-N7</v>
+        <v>S2-0 (15g)-N7</v>
       </c>
       <c r="E78" t="str">
         <v>铅头钩</v>
@@ -5663,7 +5663,7 @@
         <v>BKK</v>
       </c>
       <c r="D79" t="str">
-        <v>BHK1011-S3-0 (7.5g)-N8</v>
+        <v>S3-0 (7.5g)-N8</v>
       </c>
       <c r="E79" t="str">
         <v>铅头钩</v>
@@ -5710,7 +5710,7 @@
         <v>BKK</v>
       </c>
       <c r="D80" t="str">
-        <v>BHK1011-S3-0 (10g)-N9</v>
+        <v>S3-0 (10g)-N9</v>
       </c>
       <c r="E80" t="str">
         <v>铅头钩</v>
@@ -5757,7 +5757,7 @@
         <v>BKK</v>
       </c>
       <c r="D81" t="str">
-        <v>BHK1011-S3-0 (15g)-N10</v>
+        <v>S3-0 (15g)-N10</v>
       </c>
       <c r="E81" t="str">
         <v>铅头钩</v>
@@ -5804,7 +5804,7 @@
         <v>BKK</v>
       </c>
       <c r="D82" t="str">
-        <v>BHK1012-S1-0 (1-4 oz)-N1</v>
+        <v>S1-0 (1-4 oz)-N1</v>
       </c>
       <c r="E82" t="str">
         <v>铅头钩</v>
@@ -5851,7 +5851,7 @@
         <v>BKK</v>
       </c>
       <c r="D83" t="str">
-        <v>BHK1012-S1-0 (3-8 oz)-N2</v>
+        <v>S1-0 (3-8 oz)-N2</v>
       </c>
       <c r="E83" t="str">
         <v>铅头钩</v>
@@ -5898,7 +5898,7 @@
         <v>BKK</v>
       </c>
       <c r="D84" t="str">
-        <v>BHK1012-S3-0 (1-8 oz)-N3</v>
+        <v>S3-0 (1-8 oz)-N3</v>
       </c>
       <c r="E84" t="str">
         <v>铅头钩</v>
@@ -5945,7 +5945,7 @@
         <v>BKK</v>
       </c>
       <c r="D85" t="str">
-        <v>BHK1012-S3-0 (3-16 oz)-N4</v>
+        <v>S3-0 (3-16 oz)-N4</v>
       </c>
       <c r="E85" t="str">
         <v>铅头钩</v>
@@ -5992,7 +5992,7 @@
         <v>BKK</v>
       </c>
       <c r="D86" t="str">
-        <v>BHK1012-S3-0 (1-4oz)-N5</v>
+        <v>S3-0 (1-4oz)-N5</v>
       </c>
       <c r="E86" t="str">
         <v>铅头钩</v>
@@ -6039,7 +6039,7 @@
         <v>BKK</v>
       </c>
       <c r="D87" t="str">
-        <v>BHK1012-S3-0 (3-8 oz)-N6</v>
+        <v>S3-0 (3-8 oz)-N6</v>
       </c>
       <c r="E87" t="str">
         <v>铅头钩</v>
@@ -6086,7 +6086,7 @@
         <v>BKK</v>
       </c>
       <c r="D88" t="str">
-        <v>BHK1012-S5-0 (1-8oz)-N7</v>
+        <v>S5-0 (1-8oz)-N7</v>
       </c>
       <c r="E88" t="str">
         <v>铅头钩</v>
@@ -6133,7 +6133,7 @@
         <v>BKK</v>
       </c>
       <c r="D89" t="str">
-        <v>BHK1012-S5-0 (3-16 oz)-N8</v>
+        <v>S5-0 (3-16 oz)-N8</v>
       </c>
       <c r="E89" t="str">
         <v>铅头钩</v>
@@ -6180,7 +6180,7 @@
         <v>BKK</v>
       </c>
       <c r="D90" t="str">
-        <v>BHK1012-S5-0 (1-4 oz)-N9</v>
+        <v>S5-0 (1-4 oz)-N9</v>
       </c>
       <c r="E90" t="str">
         <v>铅头钩</v>
@@ -6227,7 +6227,7 @@
         <v>BKK</v>
       </c>
       <c r="D91" t="str">
-        <v>BHK1012-S5-0 (3-8 oz)-N10</v>
+        <v>S5-0 (3-8 oz)-N10</v>
       </c>
       <c r="E91" t="str">
         <v>铅头钩</v>
@@ -6274,7 +6274,7 @@
         <v>BKK</v>
       </c>
       <c r="D92" t="str">
-        <v>BHK1013-S1-0-N1</v>
+        <v>S1-0-N1</v>
       </c>
       <c r="E92" t="str">
         <v>铅头钩</v>
@@ -6321,7 +6321,7 @@
         <v>BKK</v>
       </c>
       <c r="D93" t="str">
-        <v>BHK1013-S2-0-N2</v>
+        <v>S2-0-N2</v>
       </c>
       <c r="E93" t="str">
         <v>铅头钩</v>
@@ -6368,7 +6368,7 @@
         <v>BKK</v>
       </c>
       <c r="D94" t="str">
-        <v>BHK1013-S3-0-N3</v>
+        <v>S3-0-N3</v>
       </c>
       <c r="E94" t="str">
         <v>铅头钩</v>
@@ -6415,7 +6415,7 @@
         <v>BKK</v>
       </c>
       <c r="D95" t="str">
-        <v>BHK1013-S4-0-N4</v>
+        <v>S4-0-N4</v>
       </c>
       <c r="E95" t="str">
         <v>铅头钩</v>
@@ -6462,7 +6462,7 @@
         <v>BKK</v>
       </c>
       <c r="D96" t="str">
-        <v>BHK1013-S5-0-N5</v>
+        <v>S5-0-N5</v>
       </c>
       <c r="E96" t="str">
         <v>铅头钩</v>
@@ -6509,7 +6509,7 @@
         <v>BKK</v>
       </c>
       <c r="D97" t="str">
-        <v>BHK1013-S6-0-N6</v>
+        <v>S6-0-N6</v>
       </c>
       <c r="E97" t="str">
         <v>铅头钩</v>
@@ -6556,7 +6556,7 @@
         <v>BKK</v>
       </c>
       <c r="D98" t="str">
-        <v>BHK1014-S1-0 (3.5g)-N1</v>
+        <v>S1-0 (3.5g)-N1</v>
       </c>
       <c r="E98" t="str">
         <v>铅头钩</v>
@@ -6603,7 +6603,7 @@
         <v>BKK</v>
       </c>
       <c r="D99" t="str">
-        <v>BHK1014-S2-0 (4.6g)-N2</v>
+        <v>S2-0 (4.6g)-N2</v>
       </c>
       <c r="E99" t="str">
         <v>铅头钩</v>
@@ -6650,7 +6650,7 @@
         <v>BKK</v>
       </c>
       <c r="D100" t="str">
-        <v>BHK1014-S3-0 (7g)-N3</v>
+        <v>S3-0 (7g)-N3</v>
       </c>
       <c r="E100" t="str">
         <v>铅头钩</v>
@@ -6697,7 +6697,7 @@
         <v>BKK</v>
       </c>
       <c r="D101" t="str">
-        <v>BHK1014-S4-0 (14g)-N4</v>
+        <v>S4-0 (14g)-N4</v>
       </c>
       <c r="E101" t="str">
         <v>铅头钩</v>
@@ -6744,7 +6744,7 @@
         <v>BKK</v>
       </c>
       <c r="D102" t="str">
-        <v>BHK1014-S5-0 (28g)-N5</v>
+        <v>S5-0 (28g)-N5</v>
       </c>
       <c r="E102" t="str">
         <v>铅头钩</v>
@@ -6791,7 +6791,7 @@
         <v>BKK</v>
       </c>
       <c r="D103" t="str">
-        <v>BHK1014-S6-0 (42g)-N6</v>
+        <v>S6-0 (42g)-N6</v>
       </c>
       <c r="E103" t="str">
         <v>铅头钩</v>
@@ -6838,7 +6838,7 @@
         <v>BKK</v>
       </c>
       <c r="D104" t="str">
-        <v>BHK1015-S1-0 (225g)-N1</v>
+        <v>S1-0 (225g)-N1</v>
       </c>
       <c r="E104" t="str">
         <v>铅头钩</v>
@@ -6885,7 +6885,7 @@
         <v>BKK</v>
       </c>
       <c r="D105" t="str">
-        <v>BHK1015-S1-0 (1.75g)-N2</v>
+        <v>S1-0 (1.75g)-N2</v>
       </c>
       <c r="E105" t="str">
         <v>铅头钩</v>
@@ -6932,7 +6932,7 @@
         <v>BKK</v>
       </c>
       <c r="D106" t="str">
-        <v>BHK1016-S6-0 (7g)-N1</v>
+        <v>S6-0 (7g)-N1</v>
       </c>
       <c r="E106" t="str">
         <v>铅头钩</v>
@@ -6979,7 +6979,7 @@
         <v>BKK</v>
       </c>
       <c r="D107" t="str">
-        <v>BHK1016-S8-0 (14g)-N2</v>
+        <v>S8-0 (14g)-N2</v>
       </c>
       <c r="E107" t="str">
         <v>铅头钩</v>
@@ -7026,7 +7026,7 @@
         <v>BKK</v>
       </c>
       <c r="D108" t="str">
-        <v>BHK1016-S10-0 (28g)-N3</v>
+        <v>S10-0 (28g)-N3</v>
       </c>
       <c r="E108" t="str">
         <v>铅头钩</v>
@@ -7073,7 +7073,7 @@
         <v>BKK</v>
       </c>
       <c r="D109" t="str">
-        <v>BHK1017-S1-0-N1</v>
+        <v>S1-0-N1</v>
       </c>
       <c r="E109" t="str">
         <v>铅头钩</v>
@@ -7120,7 +7120,7 @@
         <v>BKK</v>
       </c>
       <c r="D110" t="str">
-        <v>BHK1017-S2-0-N2</v>
+        <v>S2-0-N2</v>
       </c>
       <c r="E110" t="str">
         <v>铅头钩</v>
@@ -7167,7 +7167,7 @@
         <v>BKK</v>
       </c>
       <c r="D111" t="str">
-        <v>BHK1017-S3-0-N3</v>
+        <v>S3-0-N3</v>
       </c>
       <c r="E111" t="str">
         <v>铅头钩</v>
@@ -7214,7 +7214,7 @@
         <v>BKK</v>
       </c>
       <c r="D112" t="str">
-        <v>BHK1017-S4-0-N4</v>
+        <v>S4-0-N4</v>
       </c>
       <c r="E112" t="str">
         <v>铅头钩</v>
@@ -7261,7 +7261,7 @@
         <v>BKK</v>
       </c>
       <c r="D113" t="str">
-        <v>BHK1017-S5-0-N5</v>
+        <v>S5-0-N5</v>
       </c>
       <c r="E113" t="str">
         <v>铅头钩</v>
@@ -7308,7 +7308,7 @@
         <v>BKK</v>
       </c>
       <c r="D114" t="str">
-        <v>BHK1017-S6-0-N6</v>
+        <v>S6-0-N6</v>
       </c>
       <c r="E114" t="str">
         <v>铅头钩</v>
@@ -7355,7 +7355,7 @@
         <v>BKK</v>
       </c>
       <c r="D115" t="str">
-        <v>BHK1018-S1-0-Q6-N1</v>
+        <v>S1-0-Q6-N1</v>
       </c>
       <c r="E115" t="str">
         <v>铅头钩</v>
@@ -7402,7 +7402,7 @@
         <v>BKK</v>
       </c>
       <c r="D116" t="str">
-        <v>BHK1018-S1-0-Q6-N2</v>
+        <v>S1-0-Q6-N2</v>
       </c>
       <c r="E116" t="str">
         <v>铅头钩</v>
@@ -7449,7 +7449,7 @@
         <v>BKK</v>
       </c>
       <c r="D117" t="str">
-        <v>BHK1018-S1-0-Q6-N3</v>
+        <v>S1-0-Q6-N3</v>
       </c>
       <c r="E117" t="str">
         <v>铅头钩</v>
@@ -7496,7 +7496,7 @@
         <v>BKK</v>
       </c>
       <c r="D118" t="str">
-        <v>BHK1018-S2-0-Q5-N4</v>
+        <v>S2-0-Q5-N4</v>
       </c>
       <c r="E118" t="str">
         <v>铅头钩</v>
@@ -7543,7 +7543,7 @@
         <v>BKK</v>
       </c>
       <c r="D119" t="str">
-        <v>BHK1018-S2-0-Q5-N5</v>
+        <v>S2-0-Q5-N5</v>
       </c>
       <c r="E119" t="str">
         <v>铅头钩</v>
@@ -7590,7 +7590,7 @@
         <v>BKK</v>
       </c>
       <c r="D120" t="str">
-        <v>BHK1018-S2-0-Q5-N6</v>
+        <v>S2-0-Q5-N6</v>
       </c>
       <c r="E120" t="str">
         <v>铅头钩</v>
@@ -7637,7 +7637,7 @@
         <v>BKK</v>
       </c>
       <c r="D121" t="str">
-        <v>BHK1018-S2-0-Q5-N7</v>
+        <v>S2-0-Q5-N7</v>
       </c>
       <c r="E121" t="str">
         <v>铅头钩</v>
@@ -7684,7 +7684,7 @@
         <v>BKK</v>
       </c>
       <c r="D122" t="str">
-        <v>BHK1018-S3-0-Q5-N8</v>
+        <v>S3-0-Q5-N8</v>
       </c>
       <c r="E122" t="str">
         <v>铅头钩</v>
@@ -7731,7 +7731,7 @@
         <v>BKK</v>
       </c>
       <c r="D123" t="str">
-        <v>BHK1018-S3-0-Q5-N9</v>
+        <v>S3-0-Q5-N9</v>
       </c>
       <c r="E123" t="str">
         <v>铅头钩</v>
@@ -7778,7 +7778,7 @@
         <v>BKK</v>
       </c>
       <c r="D124" t="str">
-        <v>BHK1018-S3-0-Q5-N10</v>
+        <v>S3-0-Q5-N10</v>
       </c>
       <c r="E124" t="str">
         <v>铅头钩</v>
@@ -7825,7 +7825,7 @@
         <v>BKK</v>
       </c>
       <c r="D125" t="str">
-        <v>BHK1018-S3-0-Q5-N11</v>
+        <v>S3-0-Q5-N11</v>
       </c>
       <c r="E125" t="str">
         <v>铅头钩</v>
@@ -7872,7 +7872,7 @@
         <v>BKK</v>
       </c>
       <c r="D126" t="str">
-        <v>BHK1018-S3-0-Q5-N12</v>
+        <v>S3-0-Q5-N12</v>
       </c>
       <c r="E126" t="str">
         <v>铅头钩</v>
@@ -7919,7 +7919,7 @@
         <v>BKK</v>
       </c>
       <c r="D127" t="str">
-        <v>BHK1018-S3-0-Q4-N13</v>
+        <v>S3-0-Q4-N13</v>
       </c>
       <c r="E127" t="str">
         <v>铅头钩</v>
@@ -7966,7 +7966,7 @@
         <v>BKK</v>
       </c>
       <c r="D128" t="str">
-        <v>BHK1018-S4-0-Q5-N14</v>
+        <v>S4-0-Q5-N14</v>
       </c>
       <c r="E128" t="str">
         <v>铅头钩</v>
@@ -8013,7 +8013,7 @@
         <v>BKK</v>
       </c>
       <c r="D129" t="str">
-        <v>BHK1018-S4-0-Q5-N15</v>
+        <v>S4-0-Q5-N15</v>
       </c>
       <c r="E129" t="str">
         <v>铅头钩</v>
@@ -8060,7 +8060,7 @@
         <v>BKK</v>
       </c>
       <c r="D130" t="str">
-        <v>BHK1018-S4-0-Q5-N16</v>
+        <v>S4-0-Q5-N16</v>
       </c>
       <c r="E130" t="str">
         <v>铅头钩</v>
@@ -8107,7 +8107,7 @@
         <v>BKK</v>
       </c>
       <c r="D131" t="str">
-        <v>BHK1018-S4-0-Q5-N17</v>
+        <v>S4-0-Q5-N17</v>
       </c>
       <c r="E131" t="str">
         <v>铅头钩</v>
@@ -8154,7 +8154,7 @@
         <v>BKK</v>
       </c>
       <c r="D132" t="str">
-        <v>BHK1018-S4-0-Q5-N18</v>
+        <v>S4-0-Q5-N18</v>
       </c>
       <c r="E132" t="str">
         <v>铅头钩</v>
@@ -8201,7 +8201,7 @@
         <v>BKK</v>
       </c>
       <c r="D133" t="str">
-        <v>BHK1018-S5-0-Q4-N19</v>
+        <v>S5-0-Q4-N19</v>
       </c>
       <c r="E133" t="str">
         <v>铅头钩</v>
@@ -8248,7 +8248,7 @@
         <v>BKK</v>
       </c>
       <c r="D134" t="str">
-        <v>BHK1018-S5-0-Q4-N20</v>
+        <v>S5-0-Q4-N20</v>
       </c>
       <c r="E134" t="str">
         <v>铅头钩</v>
@@ -8295,7 +8295,7 @@
         <v>BKK</v>
       </c>
       <c r="D135" t="str">
-        <v>BHK1018-S5-0-Q4-N21</v>
+        <v>S5-0-Q4-N21</v>
       </c>
       <c r="E135" t="str">
         <v>铅头钩</v>
@@ -8342,7 +8342,7 @@
         <v>BKK</v>
       </c>
       <c r="D136" t="str">
-        <v>BHK1018-S5-0-Q4-N22</v>
+        <v>S5-0-Q4-N22</v>
       </c>
       <c r="E136" t="str">
         <v>铅头钩</v>
@@ -8389,7 +8389,7 @@
         <v>BKK</v>
       </c>
       <c r="D137" t="str">
-        <v>BHK1018-S5-0-Q4-N23</v>
+        <v>S5-0-Q4-N23</v>
       </c>
       <c r="E137" t="str">
         <v>铅头钩</v>
@@ -8436,7 +8436,7 @@
         <v>BKK</v>
       </c>
       <c r="D138" t="str">
-        <v>BHK1018-S5-0-Q3-N24</v>
+        <v>S5-0-Q3-N24</v>
       </c>
       <c r="E138" t="str">
         <v>铅头钩</v>
@@ -8483,7 +8483,7 @@
         <v>BKK</v>
       </c>
       <c r="D139" t="str">
-        <v>BHK1018-S5-0-Q3-N25</v>
+        <v>S5-0-Q3-N25</v>
       </c>
       <c r="E139" t="str">
         <v>铅头钩</v>
@@ -8530,7 +8530,7 @@
         <v>BKK</v>
       </c>
       <c r="D140" t="str">
-        <v>BHK1018-S6-0-Q4-N26</v>
+        <v>S6-0-Q4-N26</v>
       </c>
       <c r="E140" t="str">
         <v>铅头钩</v>
@@ -8577,7 +8577,7 @@
         <v>BKK</v>
       </c>
       <c r="D141" t="str">
-        <v>BHK1018-S6-0-Q4-N27</v>
+        <v>S6-0-Q4-N27</v>
       </c>
       <c r="E141" t="str">
         <v>铅头钩</v>
@@ -8624,7 +8624,7 @@
         <v>BKK</v>
       </c>
       <c r="D142" t="str">
-        <v>BHK1018-S6-0-Q4-N28</v>
+        <v>S6-0-Q4-N28</v>
       </c>
       <c r="E142" t="str">
         <v>铅头钩</v>
@@ -8671,7 +8671,7 @@
         <v>BKK</v>
       </c>
       <c r="D143" t="str">
-        <v>BHK1018-S6-0-Q3-N29</v>
+        <v>S6-0-Q3-N29</v>
       </c>
       <c r="E143" t="str">
         <v>铅头钩</v>
@@ -8718,7 +8718,7 @@
         <v>BKK</v>
       </c>
       <c r="D144" t="str">
-        <v>BHK1018-S6-0-Q3-N30</v>
+        <v>S6-0-Q3-N30</v>
       </c>
       <c r="E144" t="str">
         <v>铅头钩</v>
@@ -8765,7 +8765,7 @@
         <v>BKK</v>
       </c>
       <c r="D145" t="str">
-        <v>BHK1018-S6-0-Q3-N31</v>
+        <v>S6-0-Q3-N31</v>
       </c>
       <c r="E145" t="str">
         <v>铅头钩</v>
@@ -8812,7 +8812,7 @@
         <v>BKK</v>
       </c>
       <c r="D146" t="str">
-        <v>BHK1018-S6-0-Q3-N32</v>
+        <v>S6-0-Q3-N32</v>
       </c>
       <c r="E146" t="str">
         <v>铅头钩</v>
@@ -8859,7 +8859,7 @@
         <v>BKK</v>
       </c>
       <c r="D147" t="str">
-        <v>BHK1019-S5-0-N1</v>
+        <v>S5-0-N1</v>
       </c>
       <c r="E147" t="str">
         <v>铅头钩</v>
@@ -8906,7 +8906,7 @@
         <v>BKK</v>
       </c>
       <c r="D148" t="str">
-        <v>BHK1019-S5-0-N2</v>
+        <v>S5-0-N2</v>
       </c>
       <c r="E148" t="str">
         <v>铅头钩</v>
@@ -8953,7 +8953,7 @@
         <v>BKK</v>
       </c>
       <c r="D149" t="str">
-        <v>BHK1019-S5-0-N3</v>
+        <v>S5-0-N3</v>
       </c>
       <c r="E149" t="str">
         <v>铅头钩</v>
@@ -9000,7 +9000,7 @@
         <v>BKK</v>
       </c>
       <c r="D150" t="str">
-        <v>BHK1019-S5-0-N4</v>
+        <v>S5-0-N4</v>
       </c>
       <c r="E150" t="str">
         <v>铅头钩</v>
@@ -9047,7 +9047,7 @@
         <v>BKK</v>
       </c>
       <c r="D151" t="str">
-        <v>BHK1019-S7-0-N5</v>
+        <v>S7-0-N5</v>
       </c>
       <c r="E151" t="str">
         <v>铅头钩</v>
@@ -9094,7 +9094,7 @@
         <v>BKK</v>
       </c>
       <c r="D152" t="str">
-        <v>BHK1019-S7-0-N6</v>
+        <v>S7-0-N6</v>
       </c>
       <c r="E152" t="str">
         <v>铅头钩</v>
@@ -9141,7 +9141,7 @@
         <v>BKK</v>
       </c>
       <c r="D153" t="str">
-        <v>BHK1019-S7-0-N7</v>
+        <v>S7-0-N7</v>
       </c>
       <c r="E153" t="str">
         <v>铅头钩</v>
@@ -9188,7 +9188,7 @@
         <v>BKK</v>
       </c>
       <c r="D154" t="str">
-        <v>BHK1019-S9-0-N8</v>
+        <v>S9-0-N8</v>
       </c>
       <c r="E154" t="str">
         <v>铅头钩</v>
@@ -9235,7 +9235,7 @@
         <v>BKK</v>
       </c>
       <c r="D155" t="str">
-        <v>BHK1019-S9-0-N9</v>
+        <v>S9-0-N9</v>
       </c>
       <c r="E155" t="str">
         <v>铅头钩</v>
@@ -9282,7 +9282,7 @@
         <v>BKK</v>
       </c>
       <c r="D156" t="str">
-        <v>BHK1019-S9-0-N10</v>
+        <v>S9-0-N10</v>
       </c>
       <c r="E156" t="str">
         <v>铅头钩</v>
@@ -9329,7 +9329,7 @@
         <v>BKK</v>
       </c>
       <c r="D157" t="str">
-        <v>BHK1020-S6-Q5-N1</v>
+        <v>S6-Q5-N1</v>
       </c>
       <c r="E157" t="str">
         <v>铅头钩</v>
@@ -9376,7 +9376,7 @@
         <v>BKK</v>
       </c>
       <c r="D158" t="str">
-        <v>BHK1020-S6-Q5-N2</v>
+        <v>S6-Q5-N2</v>
       </c>
       <c r="E158" t="str">
         <v>铅头钩</v>
@@ -9423,7 +9423,7 @@
         <v>BKK</v>
       </c>
       <c r="D159" t="str">
-        <v>BHK1020-S6-Q5-N3</v>
+        <v>S6-Q5-N3</v>
       </c>
       <c r="E159" t="str">
         <v>铅头钩</v>
@@ -9470,7 +9470,7 @@
         <v>BKK</v>
       </c>
       <c r="D160" t="str">
-        <v>BHK1020-S4-Q5-N4</v>
+        <v>S4-Q5-N4</v>
       </c>
       <c r="E160" t="str">
         <v>铅头钩</v>
@@ -9517,7 +9517,7 @@
         <v>BKK</v>
       </c>
       <c r="D161" t="str">
-        <v>BHK1020-S4-Q5-N5</v>
+        <v>S4-Q5-N5</v>
       </c>
       <c r="E161" t="str">
         <v>铅头钩</v>
@@ -9564,7 +9564,7 @@
         <v>BKK</v>
       </c>
       <c r="D162" t="str">
-        <v>BHK1020-S4-Q5-N6</v>
+        <v>S4-Q5-N6</v>
       </c>
       <c r="E162" t="str">
         <v>铅头钩</v>
@@ -9611,7 +9611,7 @@
         <v>BKK</v>
       </c>
       <c r="D163" t="str">
-        <v>BHK1020-S2-Q5-N7</v>
+        <v>S2-Q5-N7</v>
       </c>
       <c r="E163" t="str">
         <v>铅头钩</v>
@@ -9658,7 +9658,7 @@
         <v>BKK</v>
       </c>
       <c r="D164" t="str">
-        <v>BHK1020-S2-Q5-N8</v>
+        <v>S2-Q5-N8</v>
       </c>
       <c r="E164" t="str">
         <v>铅头钩</v>
@@ -9705,7 +9705,7 @@
         <v>BKK</v>
       </c>
       <c r="D165" t="str">
-        <v>BHK1020-S2-Q5-N9</v>
+        <v>S2-Q5-N9</v>
       </c>
       <c r="E165" t="str">
         <v>铅头钩</v>
@@ -9752,7 +9752,7 @@
         <v>BKK</v>
       </c>
       <c r="D166" t="str">
-        <v>BHK1021-S6-Q5-N1</v>
+        <v>S6-Q5-N1</v>
       </c>
       <c r="E166" t="str">
         <v>铅头钩</v>
@@ -9799,7 +9799,7 @@
         <v>BKK</v>
       </c>
       <c r="D167" t="str">
-        <v>BHK1021-S6-Q5-N2</v>
+        <v>S6-Q5-N2</v>
       </c>
       <c r="E167" t="str">
         <v>铅头钩</v>
@@ -9846,7 +9846,7 @@
         <v>BKK</v>
       </c>
       <c r="D168" t="str">
-        <v>BHK1021-S6-Q5-N3</v>
+        <v>S6-Q5-N3</v>
       </c>
       <c r="E168" t="str">
         <v>铅头钩</v>
@@ -9893,7 +9893,7 @@
         <v>BKK</v>
       </c>
       <c r="D169" t="str">
-        <v>BHK1021-S4-Q5-N4</v>
+        <v>S4-Q5-N4</v>
       </c>
       <c r="E169" t="str">
         <v>铅头钩</v>
@@ -9940,7 +9940,7 @@
         <v>BKK</v>
       </c>
       <c r="D170" t="str">
-        <v>BHK1021-S4-Q5-N5</v>
+        <v>S4-Q5-N5</v>
       </c>
       <c r="E170" t="str">
         <v>铅头钩</v>
@@ -9987,7 +9987,7 @@
         <v>BKK</v>
       </c>
       <c r="D171" t="str">
-        <v>BHK1021-S4-Q5-N6</v>
+        <v>S4-Q5-N6</v>
       </c>
       <c r="E171" t="str">
         <v>铅头钩</v>
@@ -10034,7 +10034,7 @@
         <v>BKK</v>
       </c>
       <c r="D172" t="str">
-        <v>BHK1021-S2-Q5-N7</v>
+        <v>S2-Q5-N7</v>
       </c>
       <c r="E172" t="str">
         <v>铅头钩</v>
@@ -10081,7 +10081,7 @@
         <v>BKK</v>
       </c>
       <c r="D173" t="str">
-        <v>BHK1021-S2-Q5-N8</v>
+        <v>S2-Q5-N8</v>
       </c>
       <c r="E173" t="str">
         <v>铅头钩</v>
@@ -10128,7 +10128,7 @@
         <v>BKK</v>
       </c>
       <c r="D174" t="str">
-        <v>BHK1022-S6-Q5-N1</v>
+        <v>S6-Q5-N1</v>
       </c>
       <c r="E174" t="str">
         <v>铅头钩</v>
@@ -10175,7 +10175,7 @@
         <v>BKK</v>
       </c>
       <c r="D175" t="str">
-        <v>BHK1022-S6-Q5-N2</v>
+        <v>S6-Q5-N2</v>
       </c>
       <c r="E175" t="str">
         <v>铅头钩</v>
@@ -10222,7 +10222,7 @@
         <v>BKK</v>
       </c>
       <c r="D176" t="str">
-        <v>BHK1022-S6-Q5-N3</v>
+        <v>S6-Q5-N3</v>
       </c>
       <c r="E176" t="str">
         <v>铅头钩</v>
@@ -10269,7 +10269,7 @@
         <v>BKK</v>
       </c>
       <c r="D177" t="str">
-        <v>BHK1022-S6-Q5-N4</v>
+        <v>S6-Q5-N4</v>
       </c>
       <c r="E177" t="str">
         <v>铅头钩</v>
@@ -10316,7 +10316,7 @@
         <v>BKK</v>
       </c>
       <c r="D178" t="str">
-        <v>BHK1022-S4-Q5-N5</v>
+        <v>S4-Q5-N5</v>
       </c>
       <c r="E178" t="str">
         <v>铅头钩</v>
@@ -10363,7 +10363,7 @@
         <v>BKK</v>
       </c>
       <c r="D179" t="str">
-        <v>BHK1022-S4-Q5-N6</v>
+        <v>S4-Q5-N6</v>
       </c>
       <c r="E179" t="str">
         <v>铅头钩</v>
@@ -10410,7 +10410,7 @@
         <v>BKK</v>
       </c>
       <c r="D180" t="str">
-        <v>BHK1022-S4-Q5-N7</v>
+        <v>S4-Q5-N7</v>
       </c>
       <c r="E180" t="str">
         <v>铅头钩</v>
@@ -10457,7 +10457,7 @@
         <v>BKK</v>
       </c>
       <c r="D181" t="str">
-        <v>BHK1023-S1-Q4-N1</v>
+        <v>S1-Q4-N1</v>
       </c>
       <c r="E181" t="str">
         <v>铅头钩</v>
@@ -10504,7 +10504,7 @@
         <v>BKK</v>
       </c>
       <c r="D182" t="str">
-        <v>BHK1023-S1-Q4-N2</v>
+        <v>S1-Q4-N2</v>
       </c>
       <c r="E182" t="str">
         <v>铅头钩</v>
@@ -10551,7 +10551,7 @@
         <v>BKK</v>
       </c>
       <c r="D183" t="str">
-        <v>BHK1023-S1-Q4-N3</v>
+        <v>S1-Q4-N3</v>
       </c>
       <c r="E183" t="str">
         <v>铅头钩</v>
@@ -10598,7 +10598,7 @@
         <v>BKK</v>
       </c>
       <c r="D184" t="str">
-        <v>BHK1023-S1-Q4-N4</v>
+        <v>S1-Q4-N4</v>
       </c>
       <c r="E184" t="str">
         <v>铅头钩</v>
@@ -10645,7 +10645,7 @@
         <v>BKK</v>
       </c>
       <c r="D185" t="str">
-        <v>BHK1023-S1-Q4-N5</v>
+        <v>S1-Q4-N5</v>
       </c>
       <c r="E185" t="str">
         <v>铅头钩</v>
@@ -10692,7 +10692,7 @@
         <v>BKK</v>
       </c>
       <c r="D186" t="str">
-        <v>BHK1023-S1-Q4-N6</v>
+        <v>S1-Q4-N6</v>
       </c>
       <c r="E186" t="str">
         <v>铅头钩</v>
@@ -10739,7 +10739,7 @@
         <v>BKK</v>
       </c>
       <c r="D187" t="str">
-        <v>BHK1023-S1-0-Q4-N7</v>
+        <v>S1-0-Q4-N7</v>
       </c>
       <c r="E187" t="str">
         <v>铅头钩</v>
@@ -10786,7 +10786,7 @@
         <v>BKK</v>
       </c>
       <c r="D188" t="str">
-        <v>BHK1023-S1-0-Q4-N8</v>
+        <v>S1-0-Q4-N8</v>
       </c>
       <c r="E188" t="str">
         <v>铅头钩</v>
@@ -10833,7 +10833,7 @@
         <v>BKK</v>
       </c>
       <c r="D189" t="str">
-        <v>BHK1023-S1-0-Q4-N9</v>
+        <v>S1-0-Q4-N9</v>
       </c>
       <c r="E189" t="str">
         <v>铅头钩</v>
@@ -10880,7 +10880,7 @@
         <v>BKK</v>
       </c>
       <c r="D190" t="str">
-        <v>BHK1023-S1-0-Q4-N10</v>
+        <v>S1-0-Q4-N10</v>
       </c>
       <c r="E190" t="str">
         <v>铅头钩</v>
@@ -10927,7 +10927,7 @@
         <v>BKK</v>
       </c>
       <c r="D191" t="str">
-        <v>BHK1023-S1-0-Q4-N11</v>
+        <v>S1-0-Q4-N11</v>
       </c>
       <c r="E191" t="str">
         <v>铅头钩</v>
@@ -10974,7 +10974,7 @@
         <v>BKK</v>
       </c>
       <c r="D192" t="str">
-        <v>BHK1023-S1-0-Q4-N12</v>
+        <v>S1-0-Q4-N12</v>
       </c>
       <c r="E192" t="str">
         <v>铅头钩</v>
@@ -11021,7 +11021,7 @@
         <v>BKK</v>
       </c>
       <c r="D193" t="str">
-        <v>BHK1023-S1-0-Q4-N13</v>
+        <v>S1-0-Q4-N13</v>
       </c>
       <c r="E193" t="str">
         <v>铅头钩</v>
@@ -11068,7 +11068,7 @@
         <v>BKK</v>
       </c>
       <c r="D194" t="str">
-        <v>BHK1023-S1-0-Q4-N14</v>
+        <v>S1-0-Q4-N14</v>
       </c>
       <c r="E194" t="str">
         <v>铅头钩</v>
@@ -11115,7 +11115,7 @@
         <v>BKK</v>
       </c>
       <c r="D195" t="str">
-        <v>BHK1023-S1-Q3-N15</v>
+        <v>S1-Q3-N15</v>
       </c>
       <c r="E195" t="str">
         <v>铅头钩</v>
@@ -11162,7 +11162,7 @@
         <v>BKK</v>
       </c>
       <c r="D196" t="str">
-        <v>BHK1023-S1-Q3-N16</v>
+        <v>S1-Q3-N16</v>
       </c>
       <c r="E196" t="str">
         <v>铅头钩</v>
@@ -11209,7 +11209,7 @@
         <v>BKK</v>
       </c>
       <c r="D197" t="str">
-        <v>BHK1023-S1-Q3-N17</v>
+        <v>S1-Q3-N17</v>
       </c>
       <c r="E197" t="str">
         <v>铅头钩</v>
@@ -11256,7 +11256,7 @@
         <v>BKK</v>
       </c>
       <c r="D198" t="str">
-        <v>BHK1023-S1-Q3-N18</v>
+        <v>S1-Q3-N18</v>
       </c>
       <c r="E198" t="str">
         <v>铅头钩</v>
@@ -11303,7 +11303,7 @@
         <v>BKK</v>
       </c>
       <c r="D199" t="str">
-        <v>BHK1023-S1-Q3-N19</v>
+        <v>S1-Q3-N19</v>
       </c>
       <c r="E199" t="str">
         <v>铅头钩</v>
@@ -11350,7 +11350,7 @@
         <v>BKK</v>
       </c>
       <c r="D200" t="str">
-        <v>BHK1023-S1-Q3-N20</v>
+        <v>S1-Q3-N20</v>
       </c>
       <c r="E200" t="str">
         <v>铅头钩</v>
@@ -11397,7 +11397,7 @@
         <v>BKK</v>
       </c>
       <c r="D201" t="str">
-        <v>BHK1023-S1-0-Q3-N21</v>
+        <v>S1-0-Q3-N21</v>
       </c>
       <c r="E201" t="str">
         <v>铅头钩</v>
@@ -11444,7 +11444,7 @@
         <v>BKK</v>
       </c>
       <c r="D202" t="str">
-        <v>BHK1023-S1-0-Q3-N22</v>
+        <v>S1-0-Q3-N22</v>
       </c>
       <c r="E202" t="str">
         <v>铅头钩</v>
@@ -11491,7 +11491,7 @@
         <v>BKK</v>
       </c>
       <c r="D203" t="str">
-        <v>BHK1023-S1-0-Q3-N23</v>
+        <v>S1-0-Q3-N23</v>
       </c>
       <c r="E203" t="str">
         <v>铅头钩</v>
@@ -11538,7 +11538,7 @@
         <v>BKK</v>
       </c>
       <c r="D204" t="str">
-        <v>BHK1023-S1-0-Q3-N24</v>
+        <v>S1-0-Q3-N24</v>
       </c>
       <c r="E204" t="str">
         <v>铅头钩</v>
@@ -11585,7 +11585,7 @@
         <v>BKK</v>
       </c>
       <c r="D205" t="str">
-        <v>BHK1023-S1-0-Q3-N25</v>
+        <v>S1-0-Q3-N25</v>
       </c>
       <c r="E205" t="str">
         <v>铅头钩</v>
@@ -11632,7 +11632,7 @@
         <v>BKK</v>
       </c>
       <c r="D206" t="str">
-        <v>BHK1023-S1-0-Q3-N26</v>
+        <v>S1-0-Q3-N26</v>
       </c>
       <c r="E206" t="str">
         <v>铅头钩</v>
@@ -11679,7 +11679,7 @@
         <v>BKK</v>
       </c>
       <c r="D207" t="str">
-        <v>BHK1023-S1-0-Q3-N27</v>
+        <v>S1-0-Q3-N27</v>
       </c>
       <c r="E207" t="str">
         <v>铅头钩</v>
@@ -11726,7 +11726,7 @@
         <v>BKK</v>
       </c>
       <c r="D208" t="str">
-        <v>BHK1023-S1-0-Q3-N28</v>
+        <v>S1-0-Q3-N28</v>
       </c>
       <c r="E208" t="str">
         <v>铅头钩</v>
@@ -11773,7 +11773,7 @@
         <v>BKK</v>
       </c>
       <c r="D209" t="str">
-        <v>BHK1023-S1-Q4-N29</v>
+        <v>S1-Q4-N29</v>
       </c>
       <c r="E209" t="str">
         <v>铅头钩</v>
@@ -11820,7 +11820,7 @@
         <v>BKK</v>
       </c>
       <c r="D210" t="str">
-        <v>BHK1023-S1-Q4-N30</v>
+        <v>S1-Q4-N30</v>
       </c>
       <c r="E210" t="str">
         <v>铅头钩</v>
@@ -11867,7 +11867,7 @@
         <v>BKK</v>
       </c>
       <c r="D211" t="str">
-        <v>BHK1023-S1-Q4-N31</v>
+        <v>S1-Q4-N31</v>
       </c>
       <c r="E211" t="str">
         <v>铅头钩</v>
@@ -11914,7 +11914,7 @@
         <v>BKK</v>
       </c>
       <c r="D212" t="str">
-        <v>BHK1023-S1-0-Q4-N32</v>
+        <v>S1-0-Q4-N32</v>
       </c>
       <c r="E212" t="str">
         <v>铅头钩</v>
@@ -11961,7 +11961,7 @@
         <v>BKK</v>
       </c>
       <c r="D213" t="str">
-        <v>BHK1023-S1-0-Q4-N33</v>
+        <v>S1-0-Q4-N33</v>
       </c>
       <c r="E213" t="str">
         <v>铅头钩</v>
@@ -12008,7 +12008,7 @@
         <v>BKK</v>
       </c>
       <c r="D214" t="str">
-        <v>BHK1023-S1-0-Q4-N34</v>
+        <v>S1-0-Q4-N34</v>
       </c>
       <c r="E214" t="str">
         <v>铅头钩</v>
@@ -12055,7 +12055,7 @@
         <v>BKK</v>
       </c>
       <c r="D215" t="str">
-        <v>BHK1023-S1-0-Q4-N35</v>
+        <v>S1-0-Q4-N35</v>
       </c>
       <c r="E215" t="str">
         <v>铅头钩</v>
@@ -12102,7 +12102,7 @@
         <v>BKK</v>
       </c>
       <c r="D216" t="str">
-        <v>BHK1024-S2-Q5-N1</v>
+        <v>S2-Q5-N1</v>
       </c>
       <c r="E216" t="str">
         <v>铅头钩</v>
@@ -12149,7 +12149,7 @@
         <v>BKK</v>
       </c>
       <c r="D217" t="str">
-        <v>BHK1024-S1-Q5-N2</v>
+        <v>S1-Q5-N2</v>
       </c>
       <c r="E217" t="str">
         <v>铅头钩</v>
@@ -12196,7 +12196,7 @@
         <v>BKK</v>
       </c>
       <c r="D218" t="str">
-        <v>BHK1024-S1-0-Q5-N3</v>
+        <v>S1-0-Q5-N3</v>
       </c>
       <c r="E218" t="str">
         <v>铅头钩</v>
@@ -12243,7 +12243,7 @@
         <v>BKK</v>
       </c>
       <c r="D219" t="str">
-        <v>BHK1024-S1-0-Q4-N4</v>
+        <v>S1-0-Q4-N4</v>
       </c>
       <c r="E219" t="str">
         <v>铅头钩</v>
@@ -12290,7 +12290,7 @@
         <v>BKK</v>
       </c>
       <c r="D220" t="str">
-        <v>BHK1024-S2-0-Q4-N5</v>
+        <v>S2-0-Q4-N5</v>
       </c>
       <c r="E220" t="str">
         <v>铅头钩</v>
@@ -12337,7 +12337,7 @@
         <v>BKK</v>
       </c>
       <c r="D221" t="str">
-        <v>BHK1024-S2-0-Q4-N6</v>
+        <v>S2-0-Q4-N6</v>
       </c>
       <c r="E221" t="str">
         <v>铅头钩</v>
@@ -12384,7 +12384,7 @@
         <v>BKK</v>
       </c>
       <c r="D222" t="str">
-        <v>BHK1025-S1-0-N1</v>
+        <v>S1-0-N1</v>
       </c>
       <c r="E222" t="str">
         <v>Swimbait Hooks</v>
@@ -12431,7 +12431,7 @@
         <v>BKK</v>
       </c>
       <c r="D223" t="str">
-        <v>BHK1025-S2-0-N2</v>
+        <v>S2-0-N2</v>
       </c>
       <c r="E223" t="str">
         <v>Swimbait Hooks</v>
@@ -12478,7 +12478,7 @@
         <v>BKK</v>
       </c>
       <c r="D224" t="str">
-        <v>BHK1025-S3-0-N3</v>
+        <v>S3-0-N3</v>
       </c>
       <c r="E224" t="str">
         <v>Swimbait Hooks</v>
@@ -12525,7 +12525,7 @@
         <v>BKK</v>
       </c>
       <c r="D225" t="str">
-        <v>BHK1025-S4-0-N4</v>
+        <v>S4-0-N4</v>
       </c>
       <c r="E225" t="str">
         <v>Swimbait Hooks</v>
@@ -12572,7 +12572,7 @@
         <v>BKK</v>
       </c>
       <c r="D226" t="str">
-        <v>BHK1025-S5-0-N5</v>
+        <v>S5-0-N5</v>
       </c>
       <c r="E226" t="str">
         <v>Swimbait Hooks</v>
@@ -12619,7 +12619,7 @@
         <v>BKK</v>
       </c>
       <c r="D227" t="str">
-        <v>BHK1026-S1-0-N1</v>
+        <v>S1-0-N1</v>
       </c>
       <c r="E227" t="str">
         <v>Swimbait Hooks</v>
@@ -12666,7 +12666,7 @@
         <v>BKK</v>
       </c>
       <c r="D228" t="str">
-        <v>BHK1026-S2-0-N2</v>
+        <v>S2-0-N2</v>
       </c>
       <c r="E228" t="str">
         <v>Swimbait Hooks</v>
@@ -12713,7 +12713,7 @@
         <v>BKK</v>
       </c>
       <c r="D229" t="str">
-        <v>BHK1026-S3-0-N3</v>
+        <v>S3-0-N3</v>
       </c>
       <c r="E229" t="str">
         <v>Swimbait Hooks</v>
@@ -12760,7 +12760,7 @@
         <v>BKK</v>
       </c>
       <c r="D230" t="str">
-        <v>BHK1026-S4-0-N4</v>
+        <v>S4-0-N4</v>
       </c>
       <c r="E230" t="str">
         <v>Swimbait Hooks</v>
@@ -12807,7 +12807,7 @@
         <v>BKK</v>
       </c>
       <c r="D231" t="str">
-        <v>BHK1026-S5-0-N5</v>
+        <v>S5-0-N5</v>
       </c>
       <c r="E231" t="str">
         <v>Swimbait Hooks</v>
@@ -12854,7 +12854,7 @@
         <v>BKK</v>
       </c>
       <c r="D232" t="str">
-        <v>BHK1027-S5-0-N1</v>
+        <v>S5-0-N1</v>
       </c>
       <c r="E232" t="str">
         <v>Swimbait Hooks</v>
@@ -12901,7 +12901,7 @@
         <v>BKK</v>
       </c>
       <c r="D233" t="str">
-        <v>BHK1027-S6-0-N2</v>
+        <v>S6-0-N2</v>
       </c>
       <c r="E233" t="str">
         <v>Swimbait Hooks</v>
@@ -12948,7 +12948,7 @@
         <v>BKK</v>
       </c>
       <c r="D234" t="str">
-        <v>BHK1027-S10-0-N3</v>
+        <v>S10-0-N3</v>
       </c>
       <c r="E234" t="str">
         <v>Swimbait Hooks</v>
@@ -12995,7 +12995,7 @@
         <v>BKK</v>
       </c>
       <c r="D235" t="str">
-        <v>BHK1028-S1-0-N1</v>
+        <v>S1-0-N1</v>
       </c>
       <c r="E235" t="str">
         <v>Swimbait Hooks</v>
@@ -13042,7 +13042,7 @@
         <v>BKK</v>
       </c>
       <c r="D236" t="str">
-        <v>BHK1028-S2-0-N2</v>
+        <v>S2-0-N2</v>
       </c>
       <c r="E236" t="str">
         <v>Swimbait Hooks</v>
@@ -13089,7 +13089,7 @@
         <v>BKK</v>
       </c>
       <c r="D237" t="str">
-        <v>BHK1028-S3-0-N3</v>
+        <v>S3-0-N3</v>
       </c>
       <c r="E237" t="str">
         <v>Swimbait Hooks</v>
@@ -13136,7 +13136,7 @@
         <v>BKK</v>
       </c>
       <c r="D238" t="str">
-        <v>BHK1028-S5-0-N4</v>
+        <v>S5-0-N4</v>
       </c>
       <c r="E238" t="str">
         <v>Swimbait Hooks</v>
@@ -13183,7 +13183,7 @@
         <v>BKK</v>
       </c>
       <c r="D239" t="str">
-        <v>BHK1029-S1-0-N1</v>
+        <v>S1-0-N1</v>
       </c>
       <c r="E239" t="str">
         <v>Swimbait Hooks</v>
@@ -13230,7 +13230,7 @@
         <v>BKK</v>
       </c>
       <c r="D240" t="str">
-        <v>BHK1029-S2-0-N2</v>
+        <v>S2-0-N2</v>
       </c>
       <c r="E240" t="str">
         <v>Swimbait Hooks</v>
@@ -13277,7 +13277,7 @@
         <v>BKK</v>
       </c>
       <c r="D241" t="str">
-        <v>BHK1029-S3-0-N3</v>
+        <v>S3-0-N3</v>
       </c>
       <c r="E241" t="str">
         <v>Swimbait Hooks</v>
@@ -13324,7 +13324,7 @@
         <v>BKK</v>
       </c>
       <c r="D242" t="str">
-        <v>BHK1029-S4-0-N4</v>
+        <v>S4-0-N4</v>
       </c>
       <c r="E242" t="str">
         <v>Swimbait Hooks</v>
@@ -13371,7 +13371,7 @@
         <v>BKK</v>
       </c>
       <c r="D243" t="str">
-        <v>BHK1029-S5-0-N5</v>
+        <v>S5-0-N5</v>
       </c>
       <c r="E243" t="str">
         <v>Swimbait Hooks</v>
@@ -13418,7 +13418,7 @@
         <v>BKK</v>
       </c>
       <c r="D244" t="str">
-        <v>BHK1030-S2-0-N1</v>
+        <v>S2-0-N1</v>
       </c>
       <c r="E244" t="str">
         <v>Swimbait Hooks</v>
@@ -13465,7 +13465,7 @@
         <v>BKK</v>
       </c>
       <c r="D245" t="str">
-        <v>BHK1030-S3-0-N2</v>
+        <v>S3-0-N2</v>
       </c>
       <c r="E245" t="str">
         <v>Swimbait Hooks</v>
@@ -13512,7 +13512,7 @@
         <v>BKK</v>
       </c>
       <c r="D246" t="str">
-        <v>BHK1030-S5-0-N3</v>
+        <v>S5-0-N3</v>
       </c>
       <c r="E246" t="str">
         <v>Swimbait Hooks</v>
@@ -13559,7 +13559,7 @@
         <v>BKK</v>
       </c>
       <c r="D247" t="str">
-        <v>BHK1030-S6-0-N4</v>
+        <v>S6-0-N4</v>
       </c>
       <c r="E247" t="str">
         <v>Swimbait Hooks</v>
@@ -13606,7 +13606,7 @@
         <v>BKK</v>
       </c>
       <c r="D248" t="str">
-        <v>BHK1030-S8-0-N5</v>
+        <v>S8-0-N5</v>
       </c>
       <c r="E248" t="str">
         <v>Swimbait Hooks</v>
@@ -13653,7 +13653,7 @@
         <v>BKK</v>
       </c>
       <c r="D249" t="str">
-        <v>BHK1030-S10-0-N6</v>
+        <v>S10-0-N6</v>
       </c>
       <c r="E249" t="str">
         <v>Swimbait Hooks</v>
@@ -13700,7 +13700,7 @@
         <v>BKK</v>
       </c>
       <c r="D250" t="str">
-        <v>BHK1031-S1-0-N1</v>
+        <v>S1-0-N1</v>
       </c>
       <c r="E250" t="str">
         <v>Swimbait Hooks</v>
@@ -13747,7 +13747,7 @@
         <v>BKK</v>
       </c>
       <c r="D251" t="str">
-        <v>BHK1031-S2-0-N2</v>
+        <v>S2-0-N2</v>
       </c>
       <c r="E251" t="str">
         <v>Swimbait Hooks</v>
@@ -13794,7 +13794,7 @@
         <v>BKK</v>
       </c>
       <c r="D252" t="str">
-        <v>BHK1032-S1-0-N1</v>
+        <v>S1-0-N1</v>
       </c>
       <c r="E252" t="str">
         <v>Swimbait Hooks</v>
@@ -13841,7 +13841,7 @@
         <v>BKK</v>
       </c>
       <c r="D253" t="str">
-        <v>BHK1032-S2-0-N2</v>
+        <v>S2-0-N2</v>
       </c>
       <c r="E253" t="str">
         <v>Swimbait Hooks</v>
@@ -13888,7 +13888,7 @@
         <v>BKK</v>
       </c>
       <c r="D254" t="str">
-        <v>BHK1032-S3-0-N3</v>
+        <v>S3-0-N3</v>
       </c>
       <c r="E254" t="str">
         <v>Swimbait Hooks</v>
@@ -13935,7 +13935,7 @@
         <v>BKK</v>
       </c>
       <c r="D255" t="str">
-        <v>BHK1032-S4-0-N4</v>
+        <v>S4-0-N4</v>
       </c>
       <c r="E255" t="str">
         <v>Swimbait Hooks</v>
@@ -13982,7 +13982,7 @@
         <v>BKK</v>
       </c>
       <c r="D256" t="str">
-        <v>BHK1032-S5-0-N5</v>
+        <v>S5-0-N5</v>
       </c>
       <c r="E256" t="str">
         <v>Swimbait Hooks</v>
@@ -14029,7 +14029,7 @@
         <v>BKK</v>
       </c>
       <c r="D257" t="str">
-        <v>BHK1033-S1-0-N1</v>
+        <v>S1-0-N1</v>
       </c>
       <c r="E257" t="str">
         <v>Swimbait Hooks</v>
@@ -14076,7 +14076,7 @@
         <v>BKK</v>
       </c>
       <c r="D258" t="str">
-        <v>BHK1033-S2-0-N2</v>
+        <v>S2-0-N2</v>
       </c>
       <c r="E258" t="str">
         <v>Swimbait Hooks</v>
@@ -14123,7 +14123,7 @@
         <v>BKK</v>
       </c>
       <c r="D259" t="str">
-        <v>BHK1033-S3-0-N3</v>
+        <v>S3-0-N3</v>
       </c>
       <c r="E259" t="str">
         <v>Swimbait Hooks</v>
@@ -14170,7 +14170,7 @@
         <v>BKK</v>
       </c>
       <c r="D260" t="str">
-        <v>BHK1033-S4-0-N4</v>
+        <v>S4-0-N4</v>
       </c>
       <c r="E260" t="str">
         <v>Swimbait Hooks</v>
@@ -14217,7 +14217,7 @@
         <v>BKK</v>
       </c>
       <c r="D261" t="str">
-        <v>BHK1033-S5-0-N5</v>
+        <v>S5-0-N5</v>
       </c>
       <c r="E261" t="str">
         <v>Swimbait Hooks</v>
@@ -14264,7 +14264,7 @@
         <v>BKK</v>
       </c>
       <c r="D262" t="str">
-        <v>BHK1034-S1-0-N1</v>
+        <v>S1-0-N1</v>
       </c>
       <c r="E262" t="str">
         <v>Swimbait Hooks</v>
@@ -14311,7 +14311,7 @@
         <v>BKK</v>
       </c>
       <c r="D263" t="str">
-        <v>BHK1034-S2-0-N2</v>
+        <v>S2-0-N2</v>
       </c>
       <c r="E263" t="str">
         <v>Swimbait Hooks</v>
@@ -14358,7 +14358,7 @@
         <v>BKK</v>
       </c>
       <c r="D264" t="str">
-        <v>BHK1034-S3-0-N3</v>
+        <v>S3-0-N3</v>
       </c>
       <c r="E264" t="str">
         <v>Swimbait Hooks</v>
@@ -14405,7 +14405,7 @@
         <v>BKK</v>
       </c>
       <c r="D265" t="str">
-        <v>BHK1034-S4-0-N4</v>
+        <v>S4-0-N4</v>
       </c>
       <c r="E265" t="str">
         <v>Swimbait Hooks</v>
@@ -14452,7 +14452,7 @@
         <v>BKK</v>
       </c>
       <c r="D266" t="str">
-        <v>BHK1034-S5-0-N5</v>
+        <v>S5-0-N5</v>
       </c>
       <c r="E266" t="str">
         <v>Swimbait Hooks</v>
@@ -14499,7 +14499,7 @@
         <v>BKK</v>
       </c>
       <c r="D267" t="str">
-        <v>BHK1034-S6-0-N6</v>
+        <v>S6-0-N6</v>
       </c>
       <c r="E267" t="str">
         <v>Swimbait Hooks</v>
@@ -14546,7 +14546,7 @@
         <v>BKK</v>
       </c>
       <c r="D268" t="str">
-        <v>BHK1035-S5-0-N1</v>
+        <v>S5-0-N1</v>
       </c>
       <c r="E268" t="str">
         <v>Swimbait Hooks</v>
@@ -14593,7 +14593,7 @@
         <v>BKK</v>
       </c>
       <c r="D269" t="str">
-        <v>BHK1035-S6-0-N2</v>
+        <v>S6-0-N2</v>
       </c>
       <c r="E269" t="str">
         <v>Swimbait Hooks</v>
@@ -14640,7 +14640,7 @@
         <v>BKK</v>
       </c>
       <c r="D270" t="str">
-        <v>BHK1035-S7-0-N3</v>
+        <v>S7-0-N3</v>
       </c>
       <c r="E270" t="str">
         <v>Swimbait Hooks</v>
@@ -14687,7 +14687,7 @@
         <v>BKK</v>
       </c>
       <c r="D271" t="str">
-        <v>BHK1035-S8-0-N4</v>
+        <v>S8-0-N4</v>
       </c>
       <c r="E271" t="str">
         <v>Swimbait Hooks</v>
@@ -14734,7 +14734,7 @@
         <v>BKK</v>
       </c>
       <c r="D272" t="str">
-        <v>BHK1036-S2-0-N1</v>
+        <v>S2-0-N1</v>
       </c>
       <c r="E272" t="str">
         <v>Swimbait Hooks</v>
@@ -14781,7 +14781,7 @@
         <v>BKK</v>
       </c>
       <c r="D273" t="str">
-        <v>BHK1036-S3-0-N2</v>
+        <v>S3-0-N2</v>
       </c>
       <c r="E273" t="str">
         <v>Swimbait Hooks</v>
@@ -14828,7 +14828,7 @@
         <v>BKK</v>
       </c>
       <c r="D274" t="str">
-        <v>BHK1036-S4-0-N3</v>
+        <v>S4-0-N3</v>
       </c>
       <c r="E274" t="str">
         <v>Swimbait Hooks</v>
@@ -14875,7 +14875,7 @@
         <v>BKK</v>
       </c>
       <c r="D275" t="str">
-        <v>BHK1036-S5-0-N4</v>
+        <v>S5-0-N4</v>
       </c>
       <c r="E275" t="str">
         <v>Swimbait Hooks</v>
@@ -14922,7 +14922,7 @@
         <v>BKK</v>
       </c>
       <c r="D276" t="str">
-        <v>BHK1037-S1-0-N1</v>
+        <v>S1-0-N1</v>
       </c>
       <c r="E276" t="str">
         <v>Swimbait Hooks</v>
@@ -14969,7 +14969,7 @@
         <v>BKK</v>
       </c>
       <c r="D277" t="str">
-        <v>BHK1037-S2-0-N2</v>
+        <v>S2-0-N2</v>
       </c>
       <c r="E277" t="str">
         <v>Swimbait Hooks</v>
@@ -15016,7 +15016,7 @@
         <v>BKK</v>
       </c>
       <c r="D278" t="str">
-        <v>BHK1037-S3-0-N3</v>
+        <v>S3-0-N3</v>
       </c>
       <c r="E278" t="str">
         <v>Swimbait Hooks</v>
@@ -15063,7 +15063,7 @@
         <v>BKK</v>
       </c>
       <c r="D279" t="str">
-        <v>BHK1038-S1-0-N1</v>
+        <v>S1-0-N1</v>
       </c>
       <c r="E279" t="str">
         <v>Swimbait Hooks</v>
@@ -15110,7 +15110,7 @@
         <v>BKK</v>
       </c>
       <c r="D280" t="str">
-        <v>BHK1038-S2-0-N2</v>
+        <v>S2-0-N2</v>
       </c>
       <c r="E280" t="str">
         <v>Swimbait Hooks</v>
@@ -15157,7 +15157,7 @@
         <v>BKK</v>
       </c>
       <c r="D281" t="str">
-        <v>BHK1039-S1-0-N1</v>
+        <v>S1-0-N1</v>
       </c>
       <c r="E281" t="str">
         <v>Swimbait Hooks</v>
@@ -15204,7 +15204,7 @@
         <v>BKK</v>
       </c>
       <c r="D282" t="str">
-        <v>BHK1039-S2-0-N2</v>
+        <v>S2-0-N2</v>
       </c>
       <c r="E282" t="str">
         <v>Swimbait Hooks</v>
@@ -15251,7 +15251,7 @@
         <v>BKK</v>
       </c>
       <c r="D283" t="str">
-        <v>BHK1039-S3-0-N3</v>
+        <v>S3-0-N3</v>
       </c>
       <c r="E283" t="str">
         <v>Swimbait Hooks</v>
@@ -15298,7 +15298,7 @@
         <v>BKK</v>
       </c>
       <c r="D284" t="str">
-        <v>BHK1039-S4-0-N4</v>
+        <v>S4-0-N4</v>
       </c>
       <c r="E284" t="str">
         <v>Swimbait Hooks</v>
@@ -15345,7 +15345,7 @@
         <v>BKK</v>
       </c>
       <c r="D285" t="str">
-        <v>BHK1039-S5-0-N5</v>
+        <v>S5-0-N5</v>
       </c>
       <c r="E285" t="str">
         <v>Swimbait Hooks</v>
@@ -15392,7 +15392,7 @@
         <v>BKK</v>
       </c>
       <c r="D286" t="str">
-        <v>BHK1040-N1</v>
+        <v>N1</v>
       </c>
       <c r="E286" t="str">
         <v>Swimbait Hooks</v>
@@ -15439,7 +15439,7 @@
         <v>BKK</v>
       </c>
       <c r="D287" t="str">
-        <v>BHK1041-S1-0-Q6-N1</v>
+        <v>S1-0-Q6-N1</v>
       </c>
       <c r="E287" t="str">
         <v>Swimbait Hooks</v>
@@ -15486,7 +15486,7 @@
         <v>BKK</v>
       </c>
       <c r="D288" t="str">
-        <v>BHK1041-S2-0-Q5-N2</v>
+        <v>S2-0-Q5-N2</v>
       </c>
       <c r="E288" t="str">
         <v>Swimbait Hooks</v>
@@ -15533,7 +15533,7 @@
         <v>BKK</v>
       </c>
       <c r="D289" t="str">
-        <v>BHK1041-S3-0-Q5-N3</v>
+        <v>S3-0-Q5-N3</v>
       </c>
       <c r="E289" t="str">
         <v>Swimbait Hooks</v>
@@ -15580,7 +15580,7 @@
         <v>BKK</v>
       </c>
       <c r="D290" t="str">
-        <v>BHK1041-S4-0-Q4-N4</v>
+        <v>S4-0-Q4-N4</v>
       </c>
       <c r="E290" t="str">
         <v>Swimbait Hooks</v>
@@ -15627,7 +15627,7 @@
         <v>BKK</v>
       </c>
       <c r="D291" t="str">
-        <v>BHK1041-S5-0-Q3-N5</v>
+        <v>S5-0-Q3-N5</v>
       </c>
       <c r="E291" t="str">
         <v>Swimbait Hooks</v>
@@ -15674,7 +15674,7 @@
         <v>BKK</v>
       </c>
       <c r="D292" t="str">
-        <v>BHK1041-S6-0-Q3-N6</v>
+        <v>S6-0-Q3-N6</v>
       </c>
       <c r="E292" t="str">
         <v>Swimbait Hooks</v>
@@ -15721,7 +15721,7 @@
         <v>BKK</v>
       </c>
       <c r="D293" t="str">
-        <v>BHK1041-S8-0-Q3-N7</v>
+        <v>S8-0-Q3-N7</v>
       </c>
       <c r="E293" t="str">
         <v>Swimbait Hooks</v>
@@ -15768,7 +15768,7 @@
         <v>BKK</v>
       </c>
       <c r="D294" t="str">
-        <v>BHK1041-S10-0-Q3-N8</v>
+        <v>S10-0-Q3-N8</v>
       </c>
       <c r="E294" t="str">
         <v>Swimbait Hooks</v>
@@ -15815,7 +15815,7 @@
         <v>BKK</v>
       </c>
       <c r="D295" t="str">
-        <v>BHK1041-S12-0-Q3-N9</v>
+        <v>S12-0-Q3-N9</v>
       </c>
       <c r="E295" t="str">
         <v>Swimbait Hooks</v>
@@ -15862,7 +15862,7 @@
         <v>BKK</v>
       </c>
       <c r="D296" t="str">
-        <v>BHK1041-S14-0-Q2-N10</v>
+        <v>S14-0-Q2-N10</v>
       </c>
       <c r="E296" t="str">
         <v>Swimbait Hooks</v>
@@ -15909,7 +15909,7 @@
         <v>BKK</v>
       </c>
       <c r="D297" t="str">
-        <v>BHK1041-S16-0-Q2-N11</v>
+        <v>S16-0-Q2-N11</v>
       </c>
       <c r="E297" t="str">
         <v>Swimbait Hooks</v>
@@ -15956,7 +15956,7 @@
         <v>BKK</v>
       </c>
       <c r="D298" t="str">
-        <v>BHK1041-S18-0-Q2-N12</v>
+        <v>S18-0-Q2-N12</v>
       </c>
       <c r="E298" t="str">
         <v>Swimbait Hooks</v>
@@ -16003,7 +16003,7 @@
         <v>BKK</v>
       </c>
       <c r="D299" t="str">
-        <v>BHK1042-S6-0-Q2-N1</v>
+        <v>S6-0-Q2-N1</v>
       </c>
       <c r="E299" t="str">
         <v>Swimbait Hooks</v>
@@ -16050,7 +16050,7 @@
         <v>BKK</v>
       </c>
       <c r="D300" t="str">
-        <v>BHK1042-S8-0-Q2-N2</v>
+        <v>S8-0-Q2-N2</v>
       </c>
       <c r="E300" t="str">
         <v>Swimbait Hooks</v>
@@ -16097,7 +16097,7 @@
         <v>BKK</v>
       </c>
       <c r="D301" t="str">
-        <v>BHK1042-S10-0-Q2-N3</v>
+        <v>S10-0-Q2-N3</v>
       </c>
       <c r="E301" t="str">
         <v>Swimbait Hooks</v>
@@ -16144,7 +16144,7 @@
         <v>BKK</v>
       </c>
       <c r="D302" t="str">
-        <v>BHK1042-S12-0-Q2-N4</v>
+        <v>S12-0-Q2-N4</v>
       </c>
       <c r="E302" t="str">
         <v>Swimbait Hooks</v>
@@ -16191,7 +16191,7 @@
         <v>BKK</v>
       </c>
       <c r="D303" t="str">
-        <v>BHK1042-S14-0-Q2-N5</v>
+        <v>S14-0-Q2-N5</v>
       </c>
       <c r="E303" t="str">
         <v>Swimbait Hooks</v>
@@ -16238,7 +16238,7 @@
         <v>BKK</v>
       </c>
       <c r="D304" t="str">
-        <v>BHK1042-S16-0-Q2-N6</v>
+        <v>S16-0-Q2-N6</v>
       </c>
       <c r="E304" t="str">
         <v>Swimbait Hooks</v>
@@ -16285,7 +16285,7 @@
         <v>BKK</v>
       </c>
       <c r="D305" t="str">
-        <v>BHK1042-S18-0-Q2-N7</v>
+        <v>S18-0-Q2-N7</v>
       </c>
       <c r="E305" t="str">
         <v>Swimbait Hooks</v>
@@ -16332,7 +16332,7 @@
         <v>BKK</v>
       </c>
       <c r="D306" t="str">
-        <v>BHK1043-S1-0-N1</v>
+        <v>S1-0-N1</v>
       </c>
       <c r="E306" t="str">
         <v>Swimbait Hooks</v>
@@ -16379,7 +16379,7 @@
         <v>BKK</v>
       </c>
       <c r="D307" t="str">
-        <v>BHK1043-S2-0-N2</v>
+        <v>S2-0-N2</v>
       </c>
       <c r="E307" t="str">
         <v>Swimbait Hooks</v>
@@ -16426,7 +16426,7 @@
         <v>BKK</v>
       </c>
       <c r="D308" t="str">
-        <v>BHK1043-S3-0-N3</v>
+        <v>S3-0-N3</v>
       </c>
       <c r="E308" t="str">
         <v>Swimbait Hooks</v>
@@ -16473,7 +16473,7 @@
         <v>BKK</v>
       </c>
       <c r="D309" t="str">
-        <v>BHK1043-S4-0-N4</v>
+        <v>S4-0-N4</v>
       </c>
       <c r="E309" t="str">
         <v>Swimbait Hooks</v>
@@ -16520,7 +16520,7 @@
         <v>BKK</v>
       </c>
       <c r="D310" t="str">
-        <v>BHK1043-S5-0-N5</v>
+        <v>S5-0-N5</v>
       </c>
       <c r="E310" t="str">
         <v>Swimbait Hooks</v>
